--- a/tahoho/example/cowork-needs-folder/同仁問題範例.xlsx
+++ b/tahoho/example/cowork-needs-folder/同仁問題範例.xlsx
@@ -1,40 +1,144 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10309"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lindingyuan/Documents/external_project/agent-skills/proposal/processing/達和環保/課程參考資料/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919E5B70-DA97-E34D-8766-DC4F81647BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>可描述您在電腦上想要用AI處裡的問題，請簡單描述處該檔案或問題的流程或規則。若有原始檔(人工出處理前)與經過人工處理(有就是您自己)後的檔案，可以一併附上。</t>
+  </si>
+  <si>
+    <t>我想利用AI來輔助編程開發python應用。透過小程式從不同的營運數據中去尋找其中的亂數關係，進而找到關聯性去作判斷推理，最終開發的程式能在有限的範圍內，幫我主動挑出有可能發生異常的設備。第一步：OT伺服器的OPC DA以及OPC UA protocol的數據模擬程式；再生成OPC DA轉OPC UA程式；然後生成OPC UA數據讀取程式以及mqtt讀取程式。第二步：再說</t>
+  </si>
+  <si>
+    <t>需要彙整及處理大量的數據資料。</t>
+  </si>
+  <si>
+    <t>目前沒有想法。想經由上課了解AI可以處理的範疇、流程、規則等要求，較能評估平時的工作可以如何透過AI協助</t>
+  </si>
+  <si>
+    <t>如何使用MCP串接數據平台上已建立之總帳資料庫，定期檢查帳務是否有異常(例如不合理的金額或項目、週期性未入項目、摘要或是分析代碼不合規)</t>
+  </si>
+  <si>
+    <t>收到廠商給的azure 明細，要依據tag建立分類表</t>
+  </si>
+  <si>
+    <t>把工單資料做成統計圖表</t>
+  </si>
+  <si>
+    <t>透過郵件進行專案管理，掌控各式文件審查，意見回覆，定期更新專案進度與狀態。</t>
+  </si>
+  <si>
+    <t>彙整各單位提案單內容，編製成董事會議程及議事錄等文件。就個案履約爭議，蒐集彙整司法實務見解、法規依據，形成法律意見書。</t>
+  </si>
+  <si>
+    <t>(查核者)現場安全衛生訪查→(查核者)撰寫報告→(查核者)寄送報告→(被查核者)上傳佐證/改善說明→(查核者)自動追蹤/(被查核者)發送提醒→(查核者)審核→結案</t>
+  </si>
+  <si>
+    <t>線上教育訓練的安排，課程有十堂，有二張帳號，有八人要輪流使用帳號去上課，一人一堂課約十個工作天，要如何安排八人二帳號十堂課的, 一個人同一時間不得上二堂課，帳號也無法共享</t>
+  </si>
+  <si>
+    <t>v主要想借AI節省尋找法院資源及整理不同判決間之意見比較之時間;實務通說意見;搜尋新聞或法院判決協助作某些主題之案例資源;相關新法/政策公告的每週提醒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.福委會經費明細表，以往需要系統進入每間公司/或是逐一打開EXCEL表，再填入福委會EXCEL計算出來，較花時間也容易錯誤，想找到更有效率的做法。2.表格經過歷任會計編輯有一些重複欄位，也想修改使表格精簡化，但需花大量時間整理，暫時只能按就表格執行例行作業。3.目前的暫借款、零用金報核，因沒有ERP可輸入此塊資料，皆是仰賴紙本親簽作業，使用AI代理人，有辦法寫出電子簽核以及自動發MAIL，讓主管於手機上可審核的介面嗎?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>對應檔案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Litzer _ DCS Tag Clarification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5(優化step1速度)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仁武資料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CostManagement_AZURE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024焚化廠維修KPI每月追蹤</t>
+  </si>
+  <si>
+    <t>2024_BL_ERP維護績效</t>
+  </si>
+  <si>
+    <t>提案單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>決議議案</t>
+  </si>
+  <si>
+    <t>訓練安排</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="新細明體"/>
+      <family val="3"/>
       <charset val="136"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -52,94 +156,69 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:B16" totalsRowShown="0">
+  <autoFilter ref="A1:B16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="2">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="可描述您在電腦上想要用AI處裡的問題，請簡單描述處該檔案或問題的流程或規則。若有原始檔(人工出處理前)與經過人工處理(有就是您自己)後的檔案，可以一併附上。" dataDxfId="0">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="ra78c7dc8afb14d42900562295928160e"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="1" xr3:uid="{BE587BAE-97E0-A54B-9202-13E6443EF886}" name="對應檔案" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <extLst>
+    <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
+      <xlmsforms:msForm id="weHr51bNlk2ZqB549M00XaAAOuuhyQ1IiV8k1Od_3fhUMVAzVzM2R0Q5SVVYVlVLU1A5NEoyTU1ESy4u" isFormConnected="1" maxResponseId="22" latestEventMarker="4">
+        <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>responder</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>responderName</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>rf443ad4e5d2f4c2cbb2f574190f59ba9</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>ra78c7dc8afb14d42900562295928160e</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r594d8b5dd5f04ef2bca2f4f9b82f3346</xlmsforms:syncedQuestionId>
+      </xlmsforms:msForm>
+    </ext>
+  </extLst>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -438,177 +517,132 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="103" customWidth="1" min="1" max="1"/>
-    <col width="73.19921875" customWidth="1" min="2" max="2"/>
-    <col width="20" bestFit="1" customWidth="1" min="3" max="6"/>
-    <col width="33.19921875" customWidth="1" min="7" max="7"/>
-    <col width="35.796875" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="73.796875" customWidth="1"/>
+    <col min="2" max="5" width="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.19921875" customWidth="1"/>
+    <col min="7" max="7" width="35.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>可描述您在電腦上想要用AI處裡的問題，請簡單描述處該檔案或問題的流程或規則。若有原始檔(人工出處理前)與經過人工處理(有就是您自己)後的檔案，可以一併附上。</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>對應的檔案</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>我想利用AI來輔助編程開發python應用。透過小程式從不同的營運數據中去尋找其中的亂數關係，進而找到關聯性去作判斷推理，最終開發的程式能在有限的範圍內，幫我主動挑出有可能發生異常的設備。第一步：OT伺服器的OPC DA以及OPC UA protocol的數據模擬程式；再生成OPC DA轉OPC UA程式；然後生成OPC UA數據讀取程式以及mqtt讀取程式。第二步：再說</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n"/>
-    </row>
-    <row r="3">
-      <c r="C3" s="1" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>需要彙整及處理大量的數據資料。</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>目前沒有想法。想經由上課了解AI可以處理的範疇、流程、規則等要求，較能評估平時的工作可以如何透過AI協助</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>如何使用MCP串接數據平台上已建立之總帳資料庫，定期檢查帳務是否有異常(例如不合理的金額或項目、週期性未入項目、摘要或是分析代碼不合規)</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>主要想借AI節省尋找法院資源及整理不同判決間之意見比較之時間;實務通說意見;搜尋新聞或法院判決協助作某些主題之案例資源;相關新法/政策公告的每週提醒</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>收到廠商給的azure 明細，要依據tag建立分類表</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1.福委會經費明細表，以往需要系統進入每間公司/或是逐一打開EXCEL表，再填入福委會EXCEL計算出來，較花時間也容易錯誤，想找到更有效率的做法。2.表格經過歷任會計編輯有一些重複欄位，也想修改使表格精簡化，但需花大量時間整理，暫時只能按就表格執行例行作業。3.目前的暫借款、零用金報核，因沒有ERP可輸入此塊資料，皆是仰賴紙本親簽作業，使用AI代理人，有辦法寫出電子簽核以及自動發MAIL，讓主管於手機上可審核的介面嗎?</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n"/>
-    </row>
-    <row r="10">
-      <c r="C10" s="1" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>把工單資料做成統計圖表</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>透過郵件進行專案管理，掌控各式文件審查，意見回覆，定期更新專案進度與狀態。</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
-    </row>
-    <row r="15">
-      <c r="C15" s="1" t="n"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="1" t="n"/>
-    </row>
-    <row r="17">
-      <c r="C17" s="1" t="n"/>
-    </row>
-    <row r="18">
-      <c r="C18" s="1" t="n"/>
-    </row>
-    <row r="19">
-      <c r="C19" s="1" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>彙整各單位提案單內容，編製成董事會議程及議事錄等文件。就個案履約爭議，蒐集彙整司法實務見解、法規依據，形成法律意見書。</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>(查核者)現場安全衛生訪查→(查核者)撰寫報告→(查核者)寄送報告→(被查核者)上傳佐證/改善說明→(查核者)自動追蹤/(被查核者)發送提醒→(查核者)審核→結案</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="n"/>
-      <c r="C21" s="1" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n"/>
-      <c r="B22" s="1" t="n"/>
-      <c r="C22" s="1" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="1" t="n"/>
-      <c r="C23" s="1" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>線上教育訓練的安排，課程有十堂，有二張帳號，有八人要輪流使用帳號去上課，一人一堂課約十個工作天，要如何安排八人二帳號十堂課的, 一個人同一時間不得上二堂課，帳號也無法共享</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="n"/>
-      <c r="C24" s="1" t="n"/>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="75">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="1:2" ht="30">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="1:2" ht="45">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="1:2" ht="15">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="105">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:2" ht="15">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" spans="1:2" ht="30">
+      <c r="A13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="3"/>
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="45">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:2" ht="45">
+      <c r="A16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>